--- a/research/traditional_assets/database/data/egypt/egypt_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_investments_asset_management.xlsx
@@ -588,124 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05815</v>
+        <v>0.00818</v>
       </c>
       <c r="E2">
-        <v>0.07490000000000001</v>
-      </c>
-      <c r="F2">
-        <v>0.01</v>
+        <v>0.00414</v>
       </c>
       <c r="G2">
-        <v>0.02854155559094592</v>
+        <v>0.04020241391511421</v>
       </c>
       <c r="H2">
-        <v>0.02854155559094592</v>
+        <v>0.04020241391511421</v>
       </c>
       <c r="I2">
-        <v>-0.06523435321951648</v>
+        <v>0.2000631279801855</v>
       </c>
       <c r="J2">
-        <v>-0.05550838274279228</v>
+        <v>0.161679972351116</v>
       </c>
       <c r="K2">
-        <v>-113.346</v>
+        <v>-41.402</v>
       </c>
       <c r="L2">
-        <v>-0.04130686636547608</v>
+        <v>-0.009301155286968342</v>
       </c>
       <c r="M2">
-        <v>20.821</v>
+        <v>8.348000000000001</v>
       </c>
       <c r="N2">
-        <v>0.04106949129139792</v>
+        <v>0.01987477084970121</v>
       </c>
       <c r="O2">
-        <v>-0.1836941753568719</v>
+        <v>-0.2016327713637023</v>
       </c>
       <c r="P2">
-        <v>20.821</v>
+        <v>8.125</v>
       </c>
       <c r="Q2">
-        <v>0.04106949129139792</v>
+        <v>0.01934385639121015</v>
       </c>
       <c r="R2">
-        <v>-0.1836941753568719</v>
+        <v>-0.1962465581372881</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.223</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.02671298514614278</v>
       </c>
       <c r="U2">
-        <v>344.324</v>
+        <v>590.317</v>
       </c>
       <c r="V2">
-        <v>0.6791802276268813</v>
+        <v>1.405416279789539</v>
       </c>
       <c r="W2">
-        <v>0.113126079447323</v>
+        <v>0.08399209486166008</v>
       </c>
       <c r="X2">
-        <v>0.08715345083881389</v>
+        <v>0.1325569699152213</v>
       </c>
       <c r="Y2">
-        <v>0.02597262860850909</v>
+        <v>-0.0485648750535612</v>
       </c>
       <c r="Z2">
-        <v>0.7414241725984223</v>
+        <v>1.135223810938637</v>
       </c>
       <c r="AA2">
-        <v>0.01805264014319421</v>
+        <v>0.03177966237440466</v>
       </c>
       <c r="AB2">
-        <v>0.08502799625390639</v>
+        <v>0.1294548355468791</v>
       </c>
       <c r="AC2">
-        <v>-0.06715890599439872</v>
+        <v>-0.09469758277825704</v>
       </c>
       <c r="AD2">
-        <v>4955.85</v>
+        <v>4376.83</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4955.85</v>
+        <v>4376.83</v>
       </c>
       <c r="AG2">
-        <v>4611.526000000001</v>
+        <v>3786.513</v>
       </c>
       <c r="AH2">
-        <v>0.9071962832383275</v>
+        <v>0.9124364688567105</v>
       </c>
       <c r="AI2">
-        <v>0.9531232270236693</v>
+        <v>0.8206699867247677</v>
       </c>
       <c r="AJ2">
-        <v>0.9009533269147811</v>
+        <v>0.9001484116529892</v>
       </c>
       <c r="AK2">
-        <v>0.9497988369741226</v>
+        <v>0.7983500891749666</v>
       </c>
       <c r="AL2">
-        <v>343.023</v>
+        <v>271.244</v>
       </c>
       <c r="AM2">
-        <v>311.5820000000001</v>
+        <v>230.005</v>
       </c>
       <c r="AN2">
-        <v>41.33284960092077</v>
+        <v>3.931423325734263</v>
       </c>
       <c r="AO2">
-        <v>-0.5218396434058357</v>
+        <v>3.283154650425447</v>
       </c>
       <c r="AP2">
-        <v>38.46111375217889</v>
+        <v>3.401179742278321</v>
       </c>
       <c r="AQ2">
-        <v>-0.5744972431013343</v>
+        <v>3.871811482359079</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B Investments Holding S.A.E. (CASE:BINV)</t>
+          <t>Arabia Investments Holding (CASE:AIH)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,44 +721,44 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="F3">
-        <v>0.01</v>
+      <c r="D3">
+        <v>0.0288</v>
       </c>
       <c r="G3">
-        <v>1.102150537634409</v>
+        <v>0.1231754161331626</v>
       </c>
       <c r="H3">
-        <v>1.102150537634409</v>
+        <v>0.1231754161331626</v>
       </c>
       <c r="I3">
-        <v>0.8279569892473118</v>
+        <v>0.1112676056338028</v>
       </c>
       <c r="J3">
-        <v>0.7080645161290322</v>
+        <v>0.07945469188913118</v>
       </c>
       <c r="K3">
-        <v>13.1</v>
+        <v>4.67</v>
       </c>
       <c r="L3">
-        <v>0.7043010752688171</v>
+        <v>0.05979513444302177</v>
       </c>
       <c r="M3">
-        <v>12.9</v>
+        <v>0.276</v>
       </c>
       <c r="N3">
-        <v>0.126594700686948</v>
+        <v>0.012</v>
       </c>
       <c r="O3">
-        <v>0.984732824427481</v>
+        <v>0.05910064239828695</v>
       </c>
       <c r="P3">
-        <v>12.9</v>
+        <v>0.276</v>
       </c>
       <c r="Q3">
-        <v>0.126594700686948</v>
+        <v>0.012</v>
       </c>
       <c r="R3">
-        <v>0.984732824427481</v>
+        <v>0.05910064239828695</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,67 +767,58 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.33</v>
+        <v>6.59</v>
       </c>
       <c r="V3">
-        <v>0.02286555446516192</v>
-      </c>
-      <c r="W3">
-        <v>0.113126079447323</v>
+        <v>0.2865217391304348</v>
       </c>
       <c r="X3">
-        <v>0.08302001710550982</v>
-      </c>
-      <c r="Y3">
-        <v>0.03010606234181315</v>
-      </c>
-      <c r="Z3">
-        <v>0.1980830670926517</v>
-      </c>
-      <c r="AA3">
-        <v>0.1402555910543131</v>
+        <v>0.5013832393983746</v>
       </c>
       <c r="AB3">
-        <v>0.08302001710550982</v>
-      </c>
-      <c r="AC3">
-        <v>0.05723557394880327</v>
+        <v>0.1571707418965381</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>126.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>126.9</v>
       </c>
       <c r="AG3">
-        <v>-2.33</v>
+        <v>120.31</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.8465643762508339</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.7549077929803688</v>
       </c>
       <c r="AJ3">
-        <v>-0.02340062267751331</v>
+        <v>0.8395087572395507</v>
       </c>
       <c r="AK3">
-        <v>-0.01846714749940557</v>
+        <v>0.7449074360720699</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>3.391</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>13.83860414394766</v>
+      </c>
+      <c r="AO3">
+        <v>2.447887323943662</v>
       </c>
       <c r="AP3">
-        <v>-0.1503225806451613</v>
+        <v>13.11995637949837</v>
+      </c>
+      <c r="AQ3">
+        <v>2.562665880271306</v>
       </c>
     </row>
     <row r="4">
@@ -850,46 +838,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0704</v>
+        <v>0.013</v>
       </c>
       <c r="E4">
-        <v>0.0334</v>
+        <v>0.00414</v>
       </c>
       <c r="G4">
-        <v>0.9108910891089109</v>
+        <v>0.855072463768116</v>
       </c>
       <c r="H4">
-        <v>0.9108910891089109</v>
+        <v>0.855072463768116</v>
       </c>
       <c r="I4">
-        <v>0.8762376237623762</v>
+        <v>0.7108695652173913</v>
       </c>
       <c r="J4">
-        <v>0.8102736678162198</v>
+        <v>0.7087787723785166</v>
       </c>
       <c r="K4">
-        <v>1.64</v>
+        <v>1.02</v>
       </c>
       <c r="L4">
-        <v>0.8118811881188118</v>
+        <v>0.7391304347826088</v>
       </c>
       <c r="M4">
-        <v>0.828</v>
+        <v>0.517</v>
       </c>
       <c r="N4">
-        <v>0.04099009900990099</v>
+        <v>0.05286298568507158</v>
       </c>
       <c r="O4">
-        <v>0.5048780487804878</v>
+        <v>0.5068627450980392</v>
       </c>
       <c r="P4">
-        <v>0.828</v>
+        <v>0.517</v>
       </c>
       <c r="Q4">
-        <v>0.04099009900990099</v>
+        <v>0.05286298568507158</v>
       </c>
       <c r="R4">
-        <v>0.5048780487804878</v>
+        <v>0.5068627450980392</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,31 +886,16 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.166</v>
+        <v>0.054</v>
       </c>
       <c r="V4">
-        <v>0.008217821782178218</v>
-      </c>
-      <c r="W4">
-        <v>0.1115646258503401</v>
+        <v>0.005521472392638037</v>
       </c>
       <c r="X4">
-        <v>0.08302001710550982</v>
-      </c>
-      <c r="Y4">
-        <v>0.02854460874483031</v>
-      </c>
-      <c r="Z4">
-        <v>0.1385079539221064</v>
-      </c>
-      <c r="AA4">
-        <v>0.1122293478461851</v>
+        <v>0.1264772451526617</v>
       </c>
       <c r="AB4">
-        <v>0.08302001710550982</v>
-      </c>
-      <c r="AC4">
-        <v>0.0292093307406753</v>
+        <v>0.1264772451526617</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -934,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-0.166</v>
+        <v>-0.054</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -943,25 +916,25 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.008285913946291306</v>
+        <v>-0.005552128315854411</v>
       </c>
       <c r="AK4">
-        <v>-0.01061788409875911</v>
+        <v>-0.004236623254354307</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.026</v>
+        <v>-0.02</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>-0.09325842696629214</v>
+        <v>-0.054989816700611</v>
       </c>
       <c r="AQ4">
-        <v>-68.07692307692308</v>
+        <v>-49.05</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Arabia Investments Holding (CASE:AIH)</t>
+          <t>QALA For Financial Investments (CASE:CCAP)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,118 +954,115 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.008399999999999999</v>
+        <v>0.573</v>
       </c>
       <c r="G5">
-        <v>0.08049751243781095</v>
+        <v>0.0335312123179668</v>
       </c>
       <c r="H5">
-        <v>0.08049751243781095</v>
+        <v>0.0335312123179668</v>
       </c>
       <c r="I5">
-        <v>0.07920398009950248</v>
+        <v>0.1998886930711437</v>
       </c>
       <c r="J5">
-        <v>0.05854207224745835</v>
+        <v>0.1755331828078537</v>
       </c>
       <c r="K5">
-        <v>6.21</v>
+        <v>-59.5</v>
       </c>
       <c r="L5">
-        <v>0.0617910447761194</v>
+        <v>-0.0137974213894815</v>
       </c>
       <c r="M5">
-        <v>0.656</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.02056426332288401</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.1056360708534622</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.656</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.02056426332288401</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.1056360708534622</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>17.5</v>
+        <v>559.3</v>
       </c>
       <c r="V5">
-        <v>0.5485893416927899</v>
+        <v>2.790918163672655</v>
       </c>
       <c r="W5">
-        <v>0.2009708737864078</v>
+        <v>0.08399209486166008</v>
       </c>
       <c r="X5">
-        <v>0.4204643340650549</v>
+        <v>1.493544439164831</v>
       </c>
       <c r="Y5">
-        <v>-0.2194934602786471</v>
+        <v>-1.409552344303171</v>
       </c>
       <c r="Z5">
-        <v>0.8262764120693907</v>
+        <v>1.255137085977065</v>
       </c>
       <c r="AA5">
-        <v>0.04837193341173694</v>
+        <v>0.220318207561729</v>
       </c>
       <c r="AB5">
-        <v>0.1068774671404815</v>
+        <v>0.1610169940934288</v>
       </c>
       <c r="AC5">
-        <v>-0.05850553372874456</v>
+        <v>0.05930121346830011</v>
       </c>
       <c r="AD5">
-        <v>204.5</v>
+        <v>4031.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>204.5</v>
+        <v>4031.8</v>
       </c>
       <c r="AG5">
-        <v>187</v>
+        <v>3472.5</v>
       </c>
       <c r="AH5">
-        <v>0.8650592216582064</v>
+        <v>0.9526487406077219</v>
       </c>
       <c r="AI5">
-        <v>0.820296831127156</v>
+        <v>0.8559358016304347</v>
       </c>
       <c r="AJ5">
-        <v>0.8542713567839195</v>
+        <v>0.9454382095891529</v>
       </c>
       <c r="AK5">
-        <v>0.8067299396031061</v>
+        <v>0.8365252583652525</v>
       </c>
       <c r="AL5">
-        <v>3.84</v>
+        <v>266.5</v>
       </c>
       <c r="AM5">
-        <v>3.655</v>
+        <v>227.5</v>
       </c>
       <c r="AN5">
-        <v>23.83449883449883</v>
+        <v>3.721776054647836</v>
       </c>
       <c r="AO5">
-        <v>2.072916666666667</v>
+        <v>3.234521575984991</v>
       </c>
       <c r="AP5">
-        <v>21.7948717948718</v>
+        <v>3.205483245638328</v>
       </c>
       <c r="AQ5">
-        <v>2.177838577291382</v>
+        <v>3.789010989010989</v>
       </c>
     </row>
     <row r="6">
@@ -1103,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arab Moltaqa Investments Company (CASE:AMIA)</t>
+          <t>Reacap Financial Investments Co. (CASE:REAC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1112,118 +1082,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0459</v>
+        <v>0.128</v>
       </c>
       <c r="E6">
-        <v>0.268</v>
+        <v>0.188</v>
       </c>
       <c r="G6">
-        <v>0.1792746113989637</v>
+        <v>0.01815126050420168</v>
       </c>
       <c r="H6">
-        <v>0.1792746113989637</v>
+        <v>0.01815126050420168</v>
       </c>
       <c r="I6">
-        <v>0.3186528497409327</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="J6">
-        <v>0.2430600204228282</v>
+        <v>0.2676072363181249</v>
       </c>
       <c r="K6">
-        <v>7.88</v>
+        <v>2.71</v>
       </c>
       <c r="L6">
-        <v>0.2041450777202072</v>
+        <v>0.2277310924369748</v>
       </c>
       <c r="M6">
-        <v>1.41</v>
+        <v>0.488</v>
       </c>
       <c r="N6">
-        <v>0.02943632567849687</v>
+        <v>0.03210526315789474</v>
       </c>
       <c r="O6">
-        <v>0.1789340101522842</v>
+        <v>0.1800738007380074</v>
       </c>
       <c r="P6">
-        <v>1.41</v>
+        <v>0.265</v>
       </c>
       <c r="Q6">
-        <v>0.02943632567849687</v>
+        <v>0.01743421052631579</v>
       </c>
       <c r="R6">
-        <v>0.1789340101522842</v>
+        <v>0.09778597785977861</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>0.223</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.4569672131147541</v>
       </c>
       <c r="U6">
-        <v>19.7</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="V6">
-        <v>0.4112734864300626</v>
+        <v>0.05322368421052632</v>
       </c>
       <c r="W6">
-        <v>0.181986143187067</v>
+        <v>0.06843434343434343</v>
       </c>
       <c r="X6">
-        <v>0.3087370927410126</v>
+        <v>0.1325569699152213</v>
       </c>
       <c r="Y6">
-        <v>-0.1267509495539456</v>
+        <v>-0.06412262648087785</v>
       </c>
       <c r="Z6">
-        <v>0.1598211328254389</v>
+        <v>0.3007328784432651</v>
       </c>
       <c r="AA6">
-        <v>0.03884612780855071</v>
+        <v>0.08047829447019678</v>
       </c>
       <c r="AB6">
-        <v>0.1053837054959222</v>
+        <v>0.1294548355468791</v>
       </c>
       <c r="AC6">
-        <v>-0.06653757768737151</v>
+        <v>-0.04897654107668231</v>
       </c>
       <c r="AD6">
-        <v>205.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>205.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG6">
-        <v>185.7</v>
+        <v>0.551</v>
       </c>
       <c r="AH6">
-        <v>0.8108961705487564</v>
+        <v>0.08212560386473432</v>
       </c>
       <c r="AI6">
-        <v>0.7690003743916136</v>
+        <v>0.03031654034774856</v>
       </c>
       <c r="AJ6">
-        <v>0.7949486301369862</v>
+        <v>0.03498190591073583</v>
       </c>
       <c r="AK6">
-        <v>0.7506063055780113</v>
+        <v>0.01250822909809085</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>0.178</v>
       </c>
       <c r="AM6">
-        <v>-0.864</v>
+        <v>-0.742</v>
       </c>
       <c r="AN6">
-        <v>15.8</v>
+        <v>0.3126436781609196</v>
+      </c>
+      <c r="AO6">
+        <v>23.59550561797753</v>
       </c>
       <c r="AP6">
-        <v>14.28461538461539</v>
+        <v>0.1266666666666667</v>
       </c>
       <c r="AQ6">
-        <v>-14.23611111111111</v>
+        <v>-5.660377358490567</v>
       </c>
     </row>
     <row r="7">
@@ -1234,7 +1207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>International Co. For Investment &amp; Development (CASE:ICID)</t>
+          <t>B Investments Holding S.A.E. (CASE:BINV)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1242,47 +1215,41 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.46</v>
-      </c>
-      <c r="E7">
-        <v>0.14</v>
-      </c>
       <c r="G7">
-        <v>0.1026086956521739</v>
+        <v>1.286585365853659</v>
       </c>
       <c r="H7">
-        <v>0.1026086956521739</v>
+        <v>1.286585365853659</v>
       </c>
       <c r="I7">
-        <v>0.05478260869565218</v>
+        <v>0.7621951219512195</v>
       </c>
       <c r="J7">
-        <v>0.05213478260869565</v>
+        <v>0.6107411639544505</v>
       </c>
       <c r="K7">
-        <v>0.579</v>
+        <v>4.96</v>
       </c>
       <c r="L7">
-        <v>0.5034782608695653</v>
+        <v>0.7560975609756098</v>
       </c>
       <c r="M7">
-        <v>0.064</v>
+        <v>4.41</v>
       </c>
       <c r="N7">
-        <v>0.004923076923076923</v>
+        <v>0.04113805970149254</v>
       </c>
       <c r="O7">
-        <v>0.1105354058721934</v>
+        <v>0.8891129032258065</v>
       </c>
       <c r="P7">
-        <v>0.064</v>
+        <v>4.41</v>
       </c>
       <c r="Q7">
-        <v>0.004923076923076923</v>
+        <v>0.04113805970149254</v>
       </c>
       <c r="R7">
-        <v>0.1105354058721934</v>
+        <v>0.8891129032258065</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1291,31 +1258,31 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.013</v>
+        <v>2.28</v>
       </c>
       <c r="V7">
-        <v>0.001</v>
+        <v>0.02126865671641791</v>
       </c>
       <c r="W7">
-        <v>0.1527704485488127</v>
+        <v>0.03853923853923854</v>
       </c>
       <c r="X7">
-        <v>0.08302001710550982</v>
+        <v>0.1264772451526617</v>
       </c>
       <c r="Y7">
-        <v>0.06975043144330284</v>
+        <v>-0.08793800661342316</v>
       </c>
       <c r="Z7">
-        <v>0.3042328042328042</v>
+        <v>0.05203458396129135</v>
       </c>
       <c r="AA7">
-        <v>0.01586111111111111</v>
+        <v>0.03177966237440466</v>
       </c>
       <c r="AB7">
-        <v>0.08302001710550982</v>
+        <v>0.1264772451526617</v>
       </c>
       <c r="AC7">
-        <v>-0.06715890599439872</v>
+        <v>-0.09469758277825704</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1327,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-0.013</v>
+        <v>-2.28</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1336,10 +1303,10 @@
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.001001001001001001</v>
+        <v>-0.02173084254670225</v>
       </c>
       <c r="AK7">
-        <v>-0.00289081609962197</v>
+        <v>-0.02196108649585822</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1351,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>-0.203125</v>
+        <v>-0.4479371316306483</v>
       </c>
     </row>
     <row r="8">
@@ -1362,7 +1329,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Reacap Financial Investments Co. (CASE:REAC)</t>
+          <t>International Co. For Investment &amp; Development (CASE:ICID)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1371,118 +1338,115 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.07769999999999999</v>
+        <v>-0.226</v>
       </c>
       <c r="E8">
-        <v>-0.04940000000000001</v>
+        <v>-0.00347</v>
       </c>
       <c r="G8">
-        <v>0.2345844504021448</v>
+        <v>0.1374570446735395</v>
       </c>
       <c r="H8">
-        <v>0.2345844504021448</v>
+        <v>0.1374570446735395</v>
       </c>
       <c r="I8">
-        <v>0.01595174262734584</v>
+        <v>0.1030927835051546</v>
       </c>
       <c r="J8">
-        <v>0.01214481137074647</v>
+        <v>0.09444482374092535</v>
       </c>
       <c r="K8">
-        <v>3.93</v>
+        <v>0.385</v>
       </c>
       <c r="L8">
-        <v>0.5268096514745308</v>
+        <v>1.323024054982818</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>0.057</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.003851351351351351</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.148051948051948</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>0.057</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.003851351351351351</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.148051948051948</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>2.48</v>
+        <v>0.019</v>
       </c>
       <c r="V8">
-        <v>0.07948717948717948</v>
+        <v>0.001283783783783784</v>
       </c>
       <c r="W8">
-        <v>0.1103932584269663</v>
+        <v>0.09897172236503855</v>
       </c>
       <c r="X8">
-        <v>0.08715345083881389</v>
+        <v>0.1264772451526617</v>
       </c>
       <c r="Y8">
-        <v>0.0232398075881524</v>
+        <v>-0.02750552278762315</v>
       </c>
       <c r="Z8">
-        <v>0.2044956140350877</v>
+        <v>0.07461538461538461</v>
       </c>
       <c r="AA8">
-        <v>0.002483560658601115</v>
+        <v>0.007047036848361352</v>
       </c>
       <c r="AB8">
-        <v>0.08502799625390639</v>
+        <v>0.1264772451526617</v>
       </c>
       <c r="AC8">
-        <v>-0.08254443559530528</v>
+        <v>-0.1194302083043004</v>
       </c>
       <c r="AD8">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>-0.0299999999999998</v>
+        <v>-0.019</v>
       </c>
       <c r="AH8">
-        <v>0.07280832095096583</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>0.04761904761904762</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>-0.0009624639076034586</v>
+        <v>-0.001285434003112103</v>
       </c>
       <c r="AK8">
-        <v>-0.000612619971411064</v>
+        <v>-0.004946628482166103</v>
       </c>
       <c r="AL8">
-        <v>0.213</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>-0.153</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>6.960227272727273</v>
-      </c>
-      <c r="AO8">
-        <v>0.5586854460093896</v>
+        <v>0</v>
       </c>
       <c r="AP8">
-        <v>-0.08522727272727218</v>
-      </c>
-      <c r="AQ8">
-        <v>-0.7777777777777778</v>
+        <v>-0.6129032258064516</v>
       </c>
     </row>
     <row r="9">
@@ -1493,7 +1457,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Al Ahly for Development &amp; Investment (CASE:AFDI)</t>
+          <t>Arab Moltaqa Investments Company (CASE:AMIA)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1502,118 +1466,118 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.0128</v>
+        <v>0.00336</v>
       </c>
       <c r="E9">
-        <v>0.07490000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="G9">
-        <v>0.7566909975669099</v>
+        <v>0.3726027397260274</v>
       </c>
       <c r="H9">
-        <v>0.7566909975669099</v>
+        <v>0.3726027397260274</v>
       </c>
       <c r="I9">
-        <v>0.5425790754257908</v>
+        <v>0.2589041095890411</v>
       </c>
       <c r="J9">
-        <v>0.3599107866991079</v>
+        <v>0.1834012966009151</v>
       </c>
       <c r="K9">
-        <v>0.614</v>
+        <v>4.61</v>
       </c>
       <c r="L9">
-        <v>0.1493917274939173</v>
+        <v>0.1263013698630137</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>2.6</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.08496732026143791</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0.5639913232104121</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>2.6</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.08496732026143791</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.5639913232104121</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>2.17</v>
+        <v>16.7</v>
       </c>
       <c r="V9">
-        <v>0.1409090909090909</v>
+        <v>0.5457516339869281</v>
       </c>
       <c r="W9">
-        <v>0.04066225165562914</v>
+        <v>0.0903921568627451</v>
       </c>
       <c r="X9">
-        <v>0.287077769795716</v>
+        <v>0.4811044817354087</v>
       </c>
       <c r="Y9">
-        <v>-0.2464155181400869</v>
+        <v>-0.3907123248726636</v>
       </c>
       <c r="Z9">
-        <v>0.05015865267268733</v>
+        <v>0.1575312904618041</v>
       </c>
       <c r="AA9">
-        <v>0.01805264014319421</v>
+        <v>0.02889144292591023</v>
       </c>
       <c r="AB9">
-        <v>0.1049436528081627</v>
+        <v>0.1569037808062732</v>
       </c>
       <c r="AC9">
-        <v>-0.08689101266496851</v>
+        <v>-0.1280123378803629</v>
       </c>
       <c r="AD9">
-        <v>59.7</v>
+        <v>159.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>59.7</v>
+        <v>159.7</v>
       </c>
       <c r="AG9">
-        <v>57.53</v>
+        <v>143</v>
       </c>
       <c r="AH9">
-        <v>0.7949400798934753</v>
+        <v>0.8392012611665791</v>
       </c>
       <c r="AI9">
-        <v>0.7753246753246754</v>
+        <v>0.7554399243140966</v>
       </c>
       <c r="AJ9">
-        <v>0.7888386123680241</v>
+        <v>0.8237327188940092</v>
       </c>
       <c r="AK9">
-        <v>0.7688093010824536</v>
+        <v>0.7344632768361582</v>
       </c>
       <c r="AL9">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>1.47</v>
+        <v>-1.14</v>
       </c>
       <c r="AN9">
-        <v>26.53333333333333</v>
-      </c>
-      <c r="AO9">
-        <v>1.517006802721088</v>
+        <v>15.81188118811881</v>
       </c>
       <c r="AP9">
-        <v>25.56888888888889</v>
+        <v>14.15841584158416</v>
       </c>
       <c r="AQ9">
-        <v>1.517006802721088</v>
+        <v>-8.289473684210526</v>
       </c>
     </row>
     <row r="10">
@@ -1624,7 +1588,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ODIN Investments (S.A.E) (CASE:ODIN)</t>
+          <t>Al Ahly for Development &amp; Investment (CASE:AFDI)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1633,112 +1597,118 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.254</v>
+        <v>-0.126</v>
+      </c>
+      <c r="E10">
+        <v>-0.509</v>
       </c>
       <c r="G10">
-        <v>-0.01042752867570386</v>
+        <v>0.3976945244956772</v>
       </c>
       <c r="H10">
-        <v>-0.01042752867570386</v>
+        <v>0.3976945244956772</v>
       </c>
       <c r="I10">
-        <v>-0.1511991657977059</v>
+        <v>0.2</v>
       </c>
       <c r="J10">
-        <v>-0.1511991657977059</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="K10">
-        <v>-0.199</v>
+        <v>0.061</v>
       </c>
       <c r="L10">
-        <v>-0.2075078206465068</v>
+        <v>0.01757925072046109</v>
       </c>
       <c r="M10">
-        <v>0.083</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.009464082098061575</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>-0.4170854271356784</v>
+        <v>-0</v>
       </c>
       <c r="P10">
-        <v>0.083</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.009464082098061575</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>-0.4170854271356784</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>0.465</v>
+        <v>4.42</v>
       </c>
       <c r="V10">
-        <v>0.05302166476624858</v>
+        <v>0.3298507462686567</v>
       </c>
       <c r="W10">
-        <v>-0.006546052631578948</v>
+        <v>0.003860759493670886</v>
       </c>
       <c r="X10">
-        <v>0.08302001710550982</v>
+        <v>0.4145035385571519</v>
       </c>
       <c r="Y10">
-        <v>-0.08956606973708878</v>
+        <v>-0.4106427790634811</v>
       </c>
       <c r="Z10">
-        <v>0.03335652173913043</v>
+        <v>0.04448717948717949</v>
       </c>
       <c r="AA10">
-        <v>-0.005043478260869565</v>
+        <v>0.004448717948717948</v>
       </c>
       <c r="AB10">
-        <v>0.08302001710550982</v>
+        <v>0.1558130226112256</v>
       </c>
       <c r="AC10">
-        <v>-0.08806349536637939</v>
+        <v>-0.1513643046625077</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>56.8</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>56.8</v>
       </c>
       <c r="AG10">
-        <v>-0.465</v>
+        <v>52.38</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>0.8091168091168091</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>0.8056737588652482</v>
       </c>
       <c r="AJ10">
-        <v>-0.0559903672486454</v>
+        <v>0.7962906658558832</v>
       </c>
       <c r="AK10">
-        <v>-0.0742218675179569</v>
+        <v>0.7926755447941888</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AN10">
-        <v>-0</v>
+        <v>75.33156498673739</v>
+      </c>
+      <c r="AO10">
+        <v>0.6871287128712871</v>
       </c>
       <c r="AP10">
-        <v>3.72</v>
+        <v>69.46949602122015</v>
+      </c>
+      <c r="AQ10">
+        <v>0.6871287128712871</v>
       </c>
     </row>
     <row r="11">
@@ -1749,7 +1719,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qalaa Holdings S.A.E. (CASE:CCAP)</t>
+          <t>ODIN Investments (S.A.E) (CASE:ODIN)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1758,118 +1728,115 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.417</v>
+        <v>-0.325</v>
       </c>
       <c r="G11">
-        <v>0.01400451256515989</v>
+        <v>-0.1839762611275964</v>
       </c>
       <c r="H11">
-        <v>0.01400451256515989</v>
+        <v>-0.1839762611275964</v>
       </c>
       <c r="I11">
-        <v>-0.0850774138333463</v>
+        <v>-0.7551928783382789</v>
       </c>
       <c r="J11">
-        <v>-0.0850774138333463</v>
+        <v>-0.7551928783382789</v>
       </c>
       <c r="K11">
-        <v>-147.1</v>
+        <v>-0.318</v>
       </c>
       <c r="L11">
-        <v>-0.05722399439819497</v>
+        <v>-0.4718100890207715</v>
       </c>
       <c r="M11">
-        <v>4.88</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.02061681453316434</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>-0.03317471108089735</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>4.88</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.02061681453316434</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>-0.03317471108089735</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>299.5</v>
+        <v>0.145</v>
       </c>
       <c r="V11">
-        <v>1.265314744402197</v>
+        <v>0.02566371681415929</v>
       </c>
       <c r="W11">
-        <v>0.2491953244113163</v>
+        <v>-0.04907407407407407</v>
       </c>
       <c r="X11">
-        <v>1.080140100927672</v>
+        <v>0.1297244068426076</v>
       </c>
       <c r="Y11">
-        <v>-0.8309447765163558</v>
+        <v>-0.1787984809166817</v>
       </c>
       <c r="Z11">
-        <v>0.8350441787941786</v>
+        <v>0.1120532003325021</v>
       </c>
       <c r="AA11">
-        <v>-0.07104339916839915</v>
+        <v>-0.08462177888611803</v>
       </c>
       <c r="AB11">
-        <v>0.1092161034655058</v>
+        <v>0.1282651533117715</v>
       </c>
       <c r="AC11">
-        <v>-0.180259502633905</v>
+        <v>-0.2128869321978895</v>
       </c>
       <c r="AD11">
-        <v>4483.8</v>
+        <v>0.27</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>4483.8</v>
+        <v>0.27</v>
       </c>
       <c r="AG11">
-        <v>4184.3</v>
+        <v>0.125</v>
       </c>
       <c r="AH11">
-        <v>0.949857006673022</v>
+        <v>0.04560810810810811</v>
       </c>
       <c r="AI11">
-        <v>1.019230769230769</v>
+        <v>0.05172413793103448</v>
       </c>
       <c r="AJ11">
-        <v>0.9464600769056775</v>
+        <v>0.02164502164502165</v>
       </c>
       <c r="AK11">
-        <v>1.020635656267532</v>
+        <v>0.02463054187192119</v>
       </c>
       <c r="AL11">
-        <v>337.5</v>
+        <v>0.006</v>
       </c>
       <c r="AM11">
-        <v>307.5</v>
+        <v>0.006</v>
       </c>
       <c r="AN11">
-        <v>57.11847133757962</v>
+        <v>-0.5590062111801243</v>
       </c>
       <c r="AO11">
-        <v>-0.648</v>
+        <v>-84.83333333333333</v>
       </c>
       <c r="AP11">
-        <v>53.3031847133758</v>
+        <v>-0.2587991718426502</v>
       </c>
       <c r="AQ11">
-        <v>-0.7112195121951219</v>
+        <v>-84.83333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/egypt/egypt_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ11"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00818</v>
+        <v>0.0505</v>
       </c>
       <c r="E2">
-        <v>0.00414</v>
+        <v>0.213</v>
+      </c>
+      <c r="F2">
+        <v>0.05</v>
       </c>
       <c r="G2">
-        <v>0.04020241391511421</v>
+        <v>0.3912560858062976</v>
       </c>
       <c r="H2">
-        <v>0.04020241391511421</v>
+        <v>0.3912560858062976</v>
       </c>
       <c r="I2">
-        <v>0.2000631279801855</v>
+        <v>0.1866002599365058</v>
       </c>
       <c r="J2">
-        <v>0.161679972351116</v>
+        <v>0.1385460127876657</v>
       </c>
       <c r="K2">
-        <v>-41.402</v>
+        <v>119.565</v>
       </c>
       <c r="L2">
-        <v>-0.009301155286968342</v>
+        <v>0.0262760469432847</v>
       </c>
       <c r="M2">
-        <v>8.348000000000001</v>
+        <v>122.337</v>
       </c>
       <c r="N2">
-        <v>0.01987477084970121</v>
+        <v>0.0921809304218093</v>
       </c>
       <c r="O2">
-        <v>-0.2016327713637023</v>
+        <v>1.023184042152804</v>
       </c>
       <c r="P2">
-        <v>8.125</v>
+        <v>112.937</v>
       </c>
       <c r="Q2">
-        <v>0.01934385639121015</v>
+        <v>0.08509803035098029</v>
       </c>
       <c r="R2">
-        <v>-0.1962465581372881</v>
+        <v>0.9445657173922133</v>
       </c>
       <c r="S2">
-        <v>0.223</v>
+        <v>9.400000000000007</v>
       </c>
       <c r="T2">
-        <v>0.02671298514614278</v>
+        <v>0.07683693404284891</v>
       </c>
       <c r="U2">
-        <v>590.317</v>
+        <v>763.26</v>
       </c>
       <c r="V2">
-        <v>1.405416279789539</v>
+        <v>0.5751164157511641</v>
       </c>
       <c r="W2">
-        <v>0.08399209486166008</v>
+        <v>0.05671347710055096</v>
       </c>
       <c r="X2">
-        <v>0.1325569699152213</v>
+        <v>0.1480746832000696</v>
       </c>
       <c r="Y2">
-        <v>-0.0485648750535612</v>
+        <v>-0.09136120609951864</v>
       </c>
       <c r="Z2">
-        <v>1.135223810938637</v>
+        <v>1.035659279594926</v>
       </c>
       <c r="AA2">
-        <v>0.03177966237440466</v>
+        <v>0.01946751379344033</v>
       </c>
       <c r="AB2">
-        <v>0.1294548355468791</v>
+        <v>0.1293548536895186</v>
       </c>
       <c r="AC2">
-        <v>-0.09469758277825704</v>
+        <v>-0.1245744815417651</v>
       </c>
       <c r="AD2">
-        <v>4376.83</v>
+        <v>4416.54</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4376.83</v>
+        <v>4416.54</v>
       </c>
       <c r="AG2">
-        <v>3786.513</v>
+        <v>3653.28</v>
       </c>
       <c r="AH2">
-        <v>0.9124364688567105</v>
+        <v>0.7689390773859267</v>
       </c>
       <c r="AI2">
-        <v>0.8206699867247677</v>
+        <v>0.6748125240647594</v>
       </c>
       <c r="AJ2">
-        <v>0.9001484116529892</v>
+        <v>0.7335284975965882</v>
       </c>
       <c r="AK2">
-        <v>0.7983500891749666</v>
+        <v>0.6318826341588285</v>
       </c>
       <c r="AL2">
-        <v>271.244</v>
+        <v>387.205</v>
       </c>
       <c r="AM2">
-        <v>230.005</v>
+        <v>239.354</v>
       </c>
       <c r="AN2">
-        <v>3.931423325734263</v>
+        <v>3.73780031618466</v>
       </c>
       <c r="AO2">
-        <v>3.283154650425447</v>
+        <v>2.192882323317106</v>
       </c>
       <c r="AP2">
-        <v>3.401179742278321</v>
+        <v>3.091839118203638</v>
       </c>
       <c r="AQ2">
-        <v>3.871811482359079</v>
+        <v>3.547444371098874</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Arabia Investments Holding (CASE:AIH)</t>
+          <t>Egypt Kuwait Holding Company (S.A.E.) (CASE:EKHO)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,103 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0288</v>
+        <v>0.131</v>
+      </c>
+      <c r="E3">
+        <v>0.077</v>
+      </c>
+      <c r="F3">
+        <v>0.05</v>
       </c>
       <c r="G3">
-        <v>0.1231754161331626</v>
+        <v>0.5529884480160723</v>
       </c>
       <c r="H3">
-        <v>0.1231754161331626</v>
+        <v>0.5529884480160723</v>
       </c>
       <c r="I3">
-        <v>0.1112676056338028</v>
+        <v>0.2437217478653943</v>
       </c>
       <c r="J3">
-        <v>0.07945469188913118</v>
+        <v>0.1813064303616584</v>
       </c>
       <c r="K3">
-        <v>4.67</v>
+        <v>138.9</v>
       </c>
       <c r="L3">
-        <v>0.05979513444302177</v>
+        <v>0.1744098442993471</v>
       </c>
       <c r="M3">
-        <v>0.276</v>
+        <v>89.31</v>
       </c>
       <c r="N3">
-        <v>0.012</v>
+        <v>0.101017984390906</v>
       </c>
       <c r="O3">
-        <v>0.05910064239828695</v>
+        <v>0.6429805615550755</v>
       </c>
       <c r="P3">
-        <v>0.276</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="Q3">
-        <v>0.012</v>
+        <v>0.0911661576744712</v>
       </c>
       <c r="R3">
-        <v>0.05910064239828695</v>
+        <v>0.5802735781137508</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>8.710000000000008</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.09752547307132468</v>
       </c>
       <c r="U3">
-        <v>6.59</v>
+        <v>378</v>
       </c>
       <c r="V3">
-        <v>0.2865217391304348</v>
+        <v>0.4275534441805225</v>
+      </c>
+      <c r="W3">
+        <v>0.2134952351675377</v>
       </c>
       <c r="X3">
-        <v>0.5013832393983746</v>
+        <v>0.174750271148916</v>
+      </c>
+      <c r="Y3">
+        <v>0.03874496401862168</v>
+      </c>
+      <c r="Z3">
+        <v>1.088870659010118</v>
+      </c>
+      <c r="AA3">
+        <v>0.1974192523106711</v>
       </c>
       <c r="AB3">
-        <v>0.1571707418965381</v>
+        <v>0.1381895319813488</v>
+      </c>
+      <c r="AC3">
+        <v>0.05922972032932228</v>
       </c>
       <c r="AD3">
-        <v>126.9</v>
+        <v>808.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>126.9</v>
+        <v>808.7</v>
       </c>
       <c r="AG3">
-        <v>120.31</v>
+        <v>430.7</v>
       </c>
       <c r="AH3">
-        <v>0.8465643762508339</v>
+        <v>0.4777292060491493</v>
       </c>
       <c r="AI3">
-        <v>0.7549077929803688</v>
+        <v>0.5597314507198228</v>
       </c>
       <c r="AJ3">
-        <v>0.8395087572395507</v>
+        <v>0.327578338910861</v>
       </c>
       <c r="AK3">
-        <v>0.7449074360720699</v>
+        <v>0.4037307836520435</v>
       </c>
       <c r="AL3">
-        <v>3.55</v>
+        <v>61.7</v>
       </c>
       <c r="AM3">
-        <v>3.391</v>
+        <v>-32.89999999999999</v>
       </c>
       <c r="AN3">
-        <v>13.83860414394766</v>
+        <v>3.133281673769857</v>
       </c>
       <c r="AO3">
-        <v>2.447887323943662</v>
+        <v>3.145867098865478</v>
       </c>
       <c r="AP3">
-        <v>13.11995637949837</v>
+        <v>1.668733049205734</v>
       </c>
       <c r="AQ3">
-        <v>2.562665880271306</v>
+        <v>-5.899696048632221</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Saudi Egyptian Investment &amp; Finance Co. S.A.E (CASE:SEIG)</t>
+          <t>QALA For Financial Investments (CASE:CCAP)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,103 +862,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.013</v>
-      </c>
-      <c r="E4">
-        <v>0.00414</v>
+        <v>0.524</v>
       </c>
       <c r="G4">
-        <v>0.855072463768116</v>
+        <v>0.3463109697584514</v>
       </c>
       <c r="H4">
-        <v>0.855072463768116</v>
+        <v>0.3463109697584514</v>
       </c>
       <c r="I4">
-        <v>0.7108695652173913</v>
+        <v>0.1739094672771639</v>
       </c>
       <c r="J4">
-        <v>0.7087787723785166</v>
+        <v>0.1288022983940847</v>
       </c>
       <c r="K4">
-        <v>1.02</v>
+        <v>-45.3</v>
       </c>
       <c r="L4">
-        <v>0.7391304347826088</v>
+        <v>-0.01242014640967291</v>
       </c>
       <c r="M4">
-        <v>0.517</v>
+        <v>4.007</v>
       </c>
       <c r="N4">
-        <v>0.05286298568507158</v>
+        <v>0.02117864693446089</v>
       </c>
       <c r="O4">
-        <v>0.5068627450980392</v>
+        <v>-0.08845474613686534</v>
       </c>
       <c r="P4">
-        <v>0.517</v>
+        <v>3.66</v>
       </c>
       <c r="Q4">
-        <v>0.05286298568507158</v>
+        <v>0.0193446088794926</v>
       </c>
       <c r="R4">
-        <v>0.5068627450980392</v>
+        <v>-0.08079470198675498</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.3469999999999995</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.08659845270776131</v>
       </c>
       <c r="U4">
-        <v>0.054</v>
+        <v>302.9</v>
       </c>
       <c r="V4">
-        <v>0.005521472392638037</v>
+        <v>1.600951374207188</v>
+      </c>
+      <c r="W4">
+        <v>0.07215673781459063</v>
       </c>
       <c r="X4">
-        <v>0.1264772451526617</v>
+        <v>1.201053296069987</v>
+      </c>
+      <c r="Y4">
+        <v>-1.128896558255396</v>
+      </c>
+      <c r="Z4">
+        <v>1.212130275839149</v>
+      </c>
+      <c r="AA4">
+        <v>0.1561251654811384</v>
       </c>
       <c r="AB4">
-        <v>0.1264772451526617</v>
+        <v>0.1618990277136664</v>
+      </c>
+      <c r="AC4">
+        <v>-0.005773862232528015</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>3322.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>3322.5</v>
       </c>
       <c r="AG4">
-        <v>-0.054</v>
+        <v>3019.6</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.946122960389555</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.7215297081306462</v>
       </c>
       <c r="AJ4">
-        <v>-0.005552128315854411</v>
+        <v>0.9410371478434306</v>
       </c>
       <c r="AK4">
-        <v>-0.004236623254354307</v>
+        <v>0.7019224063785769</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>321.9</v>
       </c>
       <c r="AM4">
-        <v>-0.02</v>
+        <v>270</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>3.684706665187978</v>
+      </c>
+      <c r="AO4">
+        <v>1.970487729108419</v>
       </c>
       <c r="AP4">
-        <v>-0.054989816700611</v>
+        <v>3.348785627148719</v>
       </c>
       <c r="AQ4">
-        <v>-49.05</v>
+        <v>2.349259259259259</v>
       </c>
     </row>
     <row r="5">
@@ -945,7 +984,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>QALA For Financial Investments (CASE:CCAP)</t>
+          <t>Saudi Egyptian Investment &amp; Finance Co. S.A.E (CASE:SEIG)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -954,115 +993,118 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.573</v>
+        <v>0.00231</v>
+      </c>
+      <c r="E5">
+        <v>-0.00787</v>
       </c>
       <c r="G5">
-        <v>0.0335312123179668</v>
+        <v>0.7917505030181087</v>
       </c>
       <c r="H5">
-        <v>0.0335312123179668</v>
+        <v>0.7917505030181087</v>
       </c>
       <c r="I5">
-        <v>0.1998886930711437</v>
+        <v>0.7092555331991951</v>
       </c>
       <c r="J5">
-        <v>0.1755331828078537</v>
+        <v>0.7073123673548137</v>
       </c>
       <c r="K5">
-        <v>-59.5</v>
+        <v>0.729</v>
       </c>
       <c r="L5">
-        <v>-0.0137974213894815</v>
+        <v>0.7334004024144869</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>0.321</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.03147058823529412</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>0.4403292181069959</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>0.321</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.03147058823529412</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>0.4403292181069959</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>559.3</v>
+        <v>0.055</v>
       </c>
       <c r="V5">
-        <v>2.790918163672655</v>
+        <v>0.005392156862745099</v>
       </c>
       <c r="W5">
-        <v>0.08399209486166008</v>
+        <v>0.05695312499999999</v>
       </c>
       <c r="X5">
-        <v>1.493544439164831</v>
+        <v>0.1183540466479839</v>
       </c>
       <c r="Y5">
-        <v>-1.409552344303171</v>
+        <v>-0.06140092164798389</v>
       </c>
       <c r="Z5">
-        <v>1.255137085977065</v>
+        <v>0.07798525027459595</v>
       </c>
       <c r="AA5">
-        <v>0.220318207561729</v>
+        <v>0.0551599319904821</v>
       </c>
       <c r="AB5">
-        <v>0.1610169940934288</v>
+        <v>0.1183540466479839</v>
       </c>
       <c r="AC5">
-        <v>0.05930121346830011</v>
+        <v>-0.06319411465750177</v>
       </c>
       <c r="AD5">
-        <v>4031.8</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>4031.8</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>3472.5</v>
+        <v>-0.055</v>
       </c>
       <c r="AH5">
-        <v>0.9526487406077219</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.8559358016304347</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>0.9454382095891529</v>
+        <v>-0.005421389847215377</v>
       </c>
       <c r="AK5">
-        <v>0.8365252583652525</v>
+        <v>-0.006148686416992733</v>
       </c>
       <c r="AL5">
-        <v>266.5</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>227.5</v>
+        <v>-0.013</v>
       </c>
       <c r="AN5">
-        <v>3.721776054647836</v>
-      </c>
-      <c r="AO5">
-        <v>3.234521575984991</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>3.205483245638328</v>
+        <v>-0.07801418439716312</v>
       </c>
       <c r="AQ5">
-        <v>3.789010989010989</v>
+        <v>-54.23076923076923</v>
       </c>
     </row>
     <row r="6">
@@ -1073,7 +1115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Reacap Financial Investments Co. (CASE:REAC)</t>
+          <t>B Investments Holding S.A.E. (CASE:BINV)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1082,121 +1124,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.128</v>
+        <v>0.215</v>
       </c>
       <c r="E6">
-        <v>0.188</v>
+        <v>0.288</v>
       </c>
       <c r="G6">
-        <v>0.01815126050420168</v>
+        <v>2.686567164179104</v>
       </c>
       <c r="H6">
-        <v>0.01815126050420168</v>
+        <v>2.686567164179104</v>
       </c>
       <c r="I6">
-        <v>0.3529411764705883</v>
+        <v>0.4009950248756219</v>
       </c>
       <c r="J6">
-        <v>0.2676072363181249</v>
+        <v>0.3031913602718116</v>
       </c>
       <c r="K6">
-        <v>2.71</v>
+        <v>20.9</v>
       </c>
       <c r="L6">
-        <v>0.2277310924369748</v>
+        <v>1.039800995024875</v>
       </c>
       <c r="M6">
-        <v>0.488</v>
+        <v>26.2</v>
       </c>
       <c r="N6">
-        <v>0.03210526315789474</v>
+        <v>0.2668024439918533</v>
       </c>
       <c r="O6">
-        <v>0.1800738007380074</v>
+        <v>1.253588516746412</v>
       </c>
       <c r="P6">
-        <v>0.265</v>
+        <v>26.2</v>
       </c>
       <c r="Q6">
-        <v>0.01743421052631579</v>
+        <v>0.2668024439918533</v>
       </c>
       <c r="R6">
-        <v>0.09778597785977861</v>
+        <v>1.253588516746412</v>
       </c>
       <c r="S6">
-        <v>0.223</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.4569672131147541</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>0.8090000000000001</v>
+        <v>62</v>
       </c>
       <c r="V6">
-        <v>0.05322368421052632</v>
+        <v>0.6313645621181263</v>
       </c>
       <c r="W6">
-        <v>0.06843434343434343</v>
+        <v>0.1585735963581183</v>
       </c>
       <c r="X6">
-        <v>0.1325569699152213</v>
+        <v>0.1213990952512233</v>
       </c>
       <c r="Y6">
-        <v>-0.06412262648087785</v>
+        <v>0.03717450110689505</v>
       </c>
       <c r="Z6">
-        <v>0.3007328784432651</v>
+        <v>0.1562621472440333</v>
       </c>
       <c r="AA6">
-        <v>0.08047829447019678</v>
+        <v>0.04737733298191257</v>
       </c>
       <c r="AB6">
-        <v>0.1294548355468791</v>
+        <v>0.1205201753976883</v>
       </c>
       <c r="AC6">
-        <v>-0.04897654107668231</v>
+        <v>-0.07314284241577576</v>
       </c>
       <c r="AD6">
-        <v>1.36</v>
+        <v>4.85</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.36</v>
+        <v>4.85</v>
       </c>
       <c r="AG6">
-        <v>0.551</v>
+        <v>-57.15</v>
       </c>
       <c r="AH6">
-        <v>0.08212560386473432</v>
+        <v>0.04706453178068899</v>
       </c>
       <c r="AI6">
-        <v>0.03031654034774856</v>
+        <v>0.05007743933918431</v>
       </c>
       <c r="AJ6">
-        <v>0.03498190591073583</v>
+        <v>-1.392204628501827</v>
       </c>
       <c r="AK6">
-        <v>0.01250822909809085</v>
+        <v>-1.639885222381635</v>
       </c>
       <c r="AL6">
-        <v>0.178</v>
+        <v>0.222</v>
       </c>
       <c r="AM6">
-        <v>-0.742</v>
+        <v>0.222</v>
       </c>
       <c r="AN6">
-        <v>0.3126436781609196</v>
+        <v>0.5980271270036991</v>
       </c>
       <c r="AO6">
-        <v>23.59550561797753</v>
+        <v>36.30630630630631</v>
       </c>
       <c r="AP6">
-        <v>0.1266666666666667</v>
+        <v>-7.046855733662146</v>
       </c>
       <c r="AQ6">
-        <v>-5.660377358490567</v>
+        <v>36.30630630630631</v>
       </c>
     </row>
     <row r="7">
@@ -1207,7 +1249,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B Investments Holding S.A.E. (CASE:BINV)</t>
+          <t>Reacap Financial Investments Co. (CASE:REAC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1215,110 +1257,119 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.0505</v>
+      </c>
       <c r="G7">
-        <v>1.286585365853659</v>
+        <v>1.366153846153846</v>
       </c>
       <c r="H7">
-        <v>1.286585365853659</v>
+        <v>1.366153846153846</v>
       </c>
       <c r="I7">
-        <v>0.7621951219512195</v>
+        <v>0.1058461538461538</v>
       </c>
       <c r="J7">
-        <v>0.6107411639544505</v>
+        <v>0.05292307692307692</v>
       </c>
       <c r="K7">
-        <v>4.96</v>
+        <v>-0.728</v>
       </c>
       <c r="L7">
-        <v>0.7560975609756098</v>
+        <v>-0.224</v>
       </c>
       <c r="M7">
-        <v>4.41</v>
+        <v>0.245</v>
       </c>
       <c r="N7">
-        <v>0.04113805970149254</v>
+        <v>0.01376404494382022</v>
       </c>
       <c r="O7">
-        <v>0.8891129032258065</v>
+        <v>-0.3365384615384616</v>
       </c>
       <c r="P7">
-        <v>4.41</v>
+        <v>0.104</v>
       </c>
       <c r="Q7">
-        <v>0.04113805970149254</v>
+        <v>0.005842696629213483</v>
       </c>
       <c r="R7">
-        <v>0.8891129032258065</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.5755102040816327</v>
       </c>
       <c r="U7">
-        <v>2.28</v>
+        <v>0.965</v>
       </c>
       <c r="V7">
-        <v>0.02126865671641791</v>
+        <v>0.05421348314606741</v>
       </c>
       <c r="W7">
-        <v>0.03853923853923854</v>
+        <v>-0.01983651226158038</v>
       </c>
       <c r="X7">
-        <v>0.1264772451526617</v>
+        <v>0.1206504993456749</v>
       </c>
       <c r="Y7">
-        <v>-0.08793800661342316</v>
+        <v>-0.1404870116072553</v>
       </c>
       <c r="Z7">
-        <v>0.05203458396129135</v>
+        <v>0.08675920982381206</v>
       </c>
       <c r="AA7">
-        <v>0.03177966237440466</v>
+        <v>0.004591564335290977</v>
       </c>
       <c r="AB7">
-        <v>0.1264772451526617</v>
+        <v>0.1198450282935444</v>
       </c>
       <c r="AC7">
-        <v>-0.09469758277825704</v>
+        <v>-0.1152534639582534</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>0.663</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>0.663</v>
       </c>
       <c r="AG7">
-        <v>-2.28</v>
+        <v>-0.3019999999999999</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.03590965715214212</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>0.02169289663972778</v>
       </c>
       <c r="AJ7">
-        <v>-0.02173084254670225</v>
+        <v>-0.01725911532746599</v>
       </c>
       <c r="AK7">
-        <v>-0.02196108649585822</v>
+        <v>-0.01020339212108926</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1.453947368421053</v>
+      </c>
+      <c r="AO7">
+        <v>2.866666666666667</v>
       </c>
       <c r="AP7">
-        <v>-0.4479371316306483</v>
+        <v>-0.6622807017543858</v>
+      </c>
+      <c r="AQ7">
+        <v>2.866666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -1329,7 +1380,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>International Co. For Investment &amp; Development (CASE:ICID)</t>
+          <t>Arabia Investments Holding (CASE:AIH)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1338,46 +1389,46 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.226</v>
+        <v>-0.0299</v>
       </c>
       <c r="E8">
-        <v>-0.00347</v>
+        <v>0.213</v>
       </c>
       <c r="G8">
-        <v>0.1374570446735395</v>
+        <v>0.1713270142180095</v>
       </c>
       <c r="H8">
-        <v>0.1374570446735395</v>
+        <v>0.1713270142180095</v>
       </c>
       <c r="I8">
-        <v>0.1030927835051546</v>
+        <v>0.1277251184834123</v>
       </c>
       <c r="J8">
-        <v>0.09444482374092535</v>
+        <v>0.08396500057002328</v>
       </c>
       <c r="K8">
-        <v>0.385</v>
+        <v>1.69</v>
       </c>
       <c r="L8">
-        <v>1.323024054982818</v>
+        <v>0.04004739336492891</v>
       </c>
       <c r="M8">
-        <v>0.057</v>
+        <v>0.522</v>
       </c>
       <c r="N8">
-        <v>0.003851351351351351</v>
+        <v>0.02485714285714286</v>
       </c>
       <c r="O8">
-        <v>0.148051948051948</v>
+        <v>0.3088757396449704</v>
       </c>
       <c r="P8">
-        <v>0.057</v>
+        <v>0.522</v>
       </c>
       <c r="Q8">
-        <v>0.003851351351351351</v>
+        <v>0.02485714285714286</v>
       </c>
       <c r="R8">
-        <v>0.148051948051948</v>
+        <v>0.3088757396449704</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1386,67 +1437,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0.019</v>
+        <v>3.49</v>
       </c>
       <c r="V8">
-        <v>0.001283783783783784</v>
+        <v>0.1661904761904762</v>
       </c>
       <c r="W8">
-        <v>0.09897172236503855</v>
+        <v>0.04668508287292817</v>
       </c>
       <c r="X8">
-        <v>0.1264772451526617</v>
+        <v>0.4454158855695882</v>
       </c>
       <c r="Y8">
-        <v>-0.02750552278762315</v>
+        <v>-0.39873080269666</v>
       </c>
       <c r="Z8">
-        <v>0.07461538461538461</v>
+        <v>0.2761057314839047</v>
       </c>
       <c r="AA8">
-        <v>0.007047036848361352</v>
+        <v>0.02318321790143275</v>
       </c>
       <c r="AB8">
-        <v>0.1264772451526617</v>
+        <v>0.1570787170267095</v>
       </c>
       <c r="AC8">
-        <v>-0.1194302083043004</v>
+        <v>-0.1338954991252768</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>111.4</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>111.4</v>
       </c>
       <c r="AG8">
-        <v>-0.019</v>
+        <v>107.91</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>0.8413897280966768</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>0.8137326515704895</v>
       </c>
       <c r="AJ8">
-        <v>-0.001285434003112103</v>
+        <v>0.8370956481265999</v>
       </c>
       <c r="AK8">
-        <v>-0.004946628482166103</v>
+        <v>0.8088599055543062</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>2.312</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>19.47552447552448</v>
+      </c>
+      <c r="AO8">
+        <v>2.173387096774194</v>
       </c>
       <c r="AP8">
-        <v>-0.6129032258064516</v>
+        <v>18.86538461538462</v>
+      </c>
+      <c r="AQ8">
+        <v>2.331314878892734</v>
       </c>
     </row>
     <row r="9">
@@ -1466,46 +1523,46 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.00336</v>
+        <v>0.132</v>
       </c>
       <c r="E9">
-        <v>0.09300000000000001</v>
+        <v>0.213</v>
       </c>
       <c r="G9">
-        <v>0.3726027397260274</v>
+        <v>0.2702702702702703</v>
       </c>
       <c r="H9">
-        <v>0.3726027397260274</v>
+        <v>0.2702702702702703</v>
       </c>
       <c r="I9">
-        <v>0.2589041095890411</v>
+        <v>0.1616216216216216</v>
       </c>
       <c r="J9">
-        <v>0.1834012966009151</v>
+        <v>0.1052816901408451</v>
       </c>
       <c r="K9">
-        <v>4.61</v>
+        <v>3.14</v>
       </c>
       <c r="L9">
-        <v>0.1263013698630137</v>
+        <v>0.08486486486486487</v>
       </c>
       <c r="M9">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="N9">
-        <v>0.08496732026143791</v>
+        <v>0.05625</v>
       </c>
       <c r="O9">
-        <v>0.5639913232104121</v>
+        <v>0.4872611464968153</v>
       </c>
       <c r="P9">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="Q9">
-        <v>0.08496732026143791</v>
+        <v>0.05625</v>
       </c>
       <c r="R9">
-        <v>0.5639913232104121</v>
+        <v>0.4872611464968153</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1514,70 +1571,70 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>16.7</v>
+        <v>8.25</v>
       </c>
       <c r="V9">
-        <v>0.5457516339869281</v>
+        <v>0.3033088235294118</v>
       </c>
       <c r="W9">
-        <v>0.0903921568627451</v>
+        <v>0.07056179775280899</v>
       </c>
       <c r="X9">
-        <v>0.4811044817354087</v>
+        <v>0.3824252226306988</v>
       </c>
       <c r="Y9">
-        <v>-0.3907123248726636</v>
+        <v>-0.3118634248778899</v>
       </c>
       <c r="Z9">
-        <v>0.1575312904618041</v>
+        <v>0.1496158511928831</v>
       </c>
       <c r="AA9">
-        <v>0.02889144292591023</v>
+        <v>0.01575180968544791</v>
       </c>
       <c r="AB9">
-        <v>0.1569037808062732</v>
+        <v>0.15566700481835</v>
       </c>
       <c r="AC9">
-        <v>-0.1280123378803629</v>
+        <v>-0.1399151951329021</v>
       </c>
       <c r="AD9">
-        <v>159.7</v>
+        <v>116.5</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>159.7</v>
+        <v>116.5</v>
       </c>
       <c r="AG9">
-        <v>143</v>
+        <v>108.25</v>
       </c>
       <c r="AH9">
-        <v>0.8392012611665791</v>
+        <v>0.8107167710508003</v>
       </c>
       <c r="AI9">
-        <v>0.7554399243140966</v>
+        <v>0.7679630850362559</v>
       </c>
       <c r="AJ9">
-        <v>0.8237327188940092</v>
+        <v>0.7991878922111481</v>
       </c>
       <c r="AK9">
-        <v>0.7344632768361582</v>
+        <v>0.7546183339142559</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1.14</v>
+        <v>-1.17</v>
       </c>
       <c r="AN9">
-        <v>15.81188118811881</v>
+        <v>17.92307692307692</v>
       </c>
       <c r="AP9">
-        <v>14.15841584158416</v>
+        <v>16.65384615384615</v>
       </c>
       <c r="AQ9">
-        <v>-8.289473684210526</v>
+        <v>-5.111111111111112</v>
       </c>
     </row>
     <row r="10">
@@ -1588,7 +1645,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Al Ahly for Development &amp; Investment (CASE:AFDI)</t>
+          <t>International Co. For Investment &amp; Development (CASE:ICID)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1597,28 +1654,28 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.126</v>
+        <v>0.0471</v>
       </c>
       <c r="E10">
-        <v>-0.509</v>
+        <v>0.358</v>
       </c>
       <c r="G10">
-        <v>0.3976945244956772</v>
+        <v>-0.01438848920863309</v>
       </c>
       <c r="H10">
-        <v>0.3976945244956772</v>
+        <v>-0.01438848920863309</v>
       </c>
       <c r="I10">
-        <v>0.2</v>
+        <v>-0.7985611510791366</v>
       </c>
       <c r="J10">
-        <v>0.09999999999999999</v>
+        <v>-0.6698674118556394</v>
       </c>
       <c r="K10">
-        <v>0.061</v>
+        <v>0.205</v>
       </c>
       <c r="L10">
-        <v>0.01757925072046109</v>
+        <v>1.474820143884892</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1642,73 +1699,67 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>4.42</v>
+        <v>0.013</v>
       </c>
       <c r="V10">
-        <v>0.3298507462686567</v>
+        <v>0.001846590909090909</v>
       </c>
       <c r="W10">
-        <v>0.003860759493670886</v>
+        <v>0.05647382920110193</v>
       </c>
       <c r="X10">
-        <v>0.4145035385571519</v>
+        <v>0.1183540466479839</v>
       </c>
       <c r="Y10">
-        <v>-0.4106427790634811</v>
+        <v>-0.06188021744688195</v>
       </c>
       <c r="Z10">
-        <v>0.04448717948717949</v>
+        <v>0.03849349210744946</v>
       </c>
       <c r="AA10">
-        <v>0.004448717948717948</v>
+        <v>-0.02578553593130265</v>
       </c>
       <c r="AB10">
-        <v>0.1558130226112256</v>
+        <v>0.1183540466479839</v>
       </c>
       <c r="AC10">
-        <v>-0.1513643046625077</v>
+        <v>-0.1441395825792865</v>
       </c>
       <c r="AD10">
-        <v>56.8</v>
+        <v>0</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>56.8</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>52.38</v>
+        <v>-0.013</v>
       </c>
       <c r="AH10">
-        <v>0.8091168091168091</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>0.8056737588652482</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>0.7962906658558832</v>
+        <v>-0.001850007115411982</v>
       </c>
       <c r="AK10">
-        <v>0.7926755447941888</v>
+        <v>-0.005124162396531336</v>
       </c>
       <c r="AL10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AN10">
-        <v>75.33156498673739</v>
-      </c>
-      <c r="AO10">
-        <v>0.6871287128712871</v>
+        <v>-0</v>
       </c>
       <c r="AP10">
-        <v>69.46949602122015</v>
-      </c>
-      <c r="AQ10">
-        <v>0.6871287128712871</v>
+        <v>0.1171171171171171</v>
       </c>
     </row>
     <row r="11">
@@ -1719,7 +1770,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ODIN Investments (S.A.E) (CASE:ODIN)</t>
+          <t>Al Ahly for Development &amp; Investment (CASE:AFDI)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1728,25 +1779,28 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.325</v>
+        <v>-0.142</v>
+      </c>
+      <c r="E11">
+        <v>0.0389</v>
       </c>
       <c r="G11">
-        <v>-0.1839762611275964</v>
+        <v>0.3401606425702811</v>
       </c>
       <c r="H11">
-        <v>-0.1839762611275964</v>
+        <v>0.3401606425702811</v>
       </c>
       <c r="I11">
-        <v>-0.7551928783382789</v>
+        <v>0.3465863453815261</v>
       </c>
       <c r="J11">
-        <v>-0.7551928783382789</v>
+        <v>0.1868847940782739</v>
       </c>
       <c r="K11">
-        <v>-0.318</v>
+        <v>0.498</v>
       </c>
       <c r="L11">
-        <v>-0.4718100890207715</v>
+        <v>0.2</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1755,7 +1809,7 @@
         <v>-0</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P11">
         <v>-0</v>
@@ -1764,79 +1818,192 @@
         <v>-0</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
       <c r="U11">
-        <v>0.145</v>
+        <v>6.88</v>
       </c>
       <c r="V11">
-        <v>0.02566371681415929</v>
+        <v>0.3698924731182796</v>
       </c>
       <c r="W11">
-        <v>-0.04907407407407407</v>
+        <v>0.03074074074074074</v>
       </c>
       <c r="X11">
-        <v>0.1297244068426076</v>
+        <v>0.2900581973298824</v>
       </c>
       <c r="Y11">
-        <v>-0.1787984809166817</v>
+        <v>-0.2593174565891417</v>
       </c>
       <c r="Z11">
-        <v>0.1120532003325021</v>
+        <v>0.03522920203735144</v>
       </c>
       <c r="AA11">
-        <v>-0.08462177888611803</v>
+        <v>0.006583802168292331</v>
       </c>
       <c r="AB11">
-        <v>0.1282651533117715</v>
+        <v>0.1537407517173517</v>
       </c>
       <c r="AC11">
-        <v>-0.2128869321978895</v>
+        <v>-0.1471569495490594</v>
       </c>
       <c r="AD11">
-        <v>0.27</v>
+        <v>51.8</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0.27</v>
+        <v>51.8</v>
       </c>
       <c r="AG11">
-        <v>0.125</v>
+        <v>44.91999999999999</v>
       </c>
       <c r="AH11">
-        <v>0.04560810810810811</v>
+        <v>0.7357954545454545</v>
       </c>
       <c r="AI11">
-        <v>0.05172413793103448</v>
+        <v>0.8512736236647495</v>
       </c>
       <c r="AJ11">
-        <v>0.02164502164502165</v>
+        <v>0.7071788413098237</v>
       </c>
       <c r="AK11">
-        <v>0.02463054187192119</v>
+        <v>0.832314248656661</v>
       </c>
       <c r="AL11">
-        <v>0.006</v>
+        <v>0.779</v>
       </c>
       <c r="AM11">
-        <v>0.006</v>
+        <v>0.779</v>
       </c>
       <c r="AN11">
-        <v>-0.5590062111801243</v>
+        <v>58.13692480359147</v>
       </c>
       <c r="AO11">
-        <v>-84.83333333333333</v>
+        <v>1.10783055198973</v>
       </c>
       <c r="AP11">
-        <v>-0.2587991718426502</v>
+        <v>50.41526374859708</v>
       </c>
       <c r="AQ11">
-        <v>-84.83333333333333</v>
+        <v>1.10783055198973</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ODIN Investments (S.A.E) (CASE:ODIN)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>-0.9658848614072496</v>
+      </c>
+      <c r="H12">
+        <v>-0.9658848614072496</v>
+      </c>
+      <c r="I12">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="J12">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="K12">
+        <v>-0.469</v>
+      </c>
+      <c r="L12">
+        <v>-1</v>
+      </c>
+      <c r="M12">
+        <v>0.202</v>
+      </c>
+      <c r="N12">
+        <v>0.003754646840148699</v>
+      </c>
+      <c r="O12">
+        <v>-0.4307036247334755</v>
+      </c>
+      <c r="P12">
+        <v>-0</v>
+      </c>
+      <c r="Q12">
+        <v>-0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0.202</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>0.707</v>
+      </c>
+      <c r="V12">
+        <v>0.01314126394052045</v>
+      </c>
+      <c r="X12">
+        <v>0.1184995876710569</v>
+      </c>
+      <c r="AB12">
+        <v>0.1184673076725522</v>
+      </c>
+      <c r="AD12">
+        <v>0.127</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0.127</v>
+      </c>
+      <c r="AG12">
+        <v>-0.58</v>
+      </c>
+      <c r="AH12">
+        <v>0.002355035510968531</v>
+      </c>
+      <c r="AI12">
+        <v>0.01860260729456569</v>
+      </c>
+      <c r="AJ12">
+        <v>-0.01089815858699737</v>
+      </c>
+      <c r="AK12">
+        <v>-0.09477124183006536</v>
+      </c>
+      <c r="AL12">
+        <v>0.004</v>
+      </c>
+      <c r="AM12">
+        <v>0.004</v>
+      </c>
+      <c r="AN12">
+        <v>-0.2629399585921325</v>
+      </c>
+      <c r="AO12">
+        <v>-134</v>
+      </c>
+      <c r="AP12">
+        <v>1.200828157349896</v>
+      </c>
+      <c r="AQ12">
+        <v>-134</v>
       </c>
     </row>
   </sheetData>
